--- a/data/trans_bre/IP7_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP7_R-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,2</t>
+          <t>-4,08; 0,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 3,12</t>
+          <t>-4,0; 2,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 0,98</t>
+          <t>-5,64; 1,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 0,51</t>
+          <t>-13,17; 0,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 178,34</t>
+          <t>-77,79; 151,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-92,06; 89,11</t>
+          <t>-90,38; 77,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,47</t>
+          <t>-100,0; 91,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,01; -0,84</t>
+          <t>-4,85; -0,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,42</t>
+          <t>-0,18; 3,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,68</t>
+          <t>-0,55; 3,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,53</t>
+          <t>-2,47; 2,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-94,96; -26,28</t>
+          <t>-100,0; -32,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,58; 1484,92</t>
+          <t>-41,04; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,63; 1082,4</t>
+          <t>-47,74; 1000,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-86,19; 418,78</t>
+          <t>-91,89; 356,68</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -0,17</t>
+          <t>-7,14; -0,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,83</t>
+          <t>-3,94; 2,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,31</t>
+          <t>-3,55; 1,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,04</t>
+          <t>-2,42; 4,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-91,21; 15,19</t>
+          <t>-89,57; 28,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-85,85; 155,72</t>
+          <t>-83,93; 192,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 133,32</t>
+          <t>-88,9; 149,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,74; 340,17</t>
+          <t>-59,05; 377,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,01</t>
+          <t>-2,85; 2,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,31</t>
+          <t>-4,55; 1,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 2,26</t>
+          <t>-3,03; 2,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 9,32</t>
+          <t>-0,61; 8,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 181,54</t>
+          <t>-62,66; 162,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,58; 98,47</t>
+          <t>-86,32; 73,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-83,57; 283,92</t>
+          <t>-82,25; 263,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 898,44</t>
+          <t>-42,98; 1054,5</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,54</t>
+          <t>-3,23; -0,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,22</t>
+          <t>-1,61; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,02</t>
+          <t>-1,45; 0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,64</t>
+          <t>-0,98; 3,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,28; -14,75</t>
+          <t>-73,33; -16,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 72,13</t>
+          <t>-49,94; 55,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 70,58</t>
+          <t>-54,2; 63,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 201,16</t>
+          <t>-37,29; 216,36</t>
         </is>
       </c>
     </row>
